--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0065.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0065.xlsx
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Có việc gì mà cậu lại đến Septimont vậy?</t>
+          <t>Có việc gì mà bạn lại đến Septimont vậy?</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Chẳng có gì đặc biệt cả. Chỉ là vài... mâu thuẫn nhỏ với Hội thôi. Haha, dù sao thì ta cũng phải ở đây mà tránh bão.</t>
+          <t>Chẳng có gì đặc biệt cả. Chỉ là vài... mâu thuẫn nhỏ với Hội thôi. Haha, dù sao thì tao cũng phải ở đây mà tránh bão.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Rồi ta nghe nói về cuộc thi đấu võ đài ở Septimont. Một sân khấu nơi vô số câu chuyện sẽ được khai sinh! Sao ta có thể bỏ lỡ chứ?</t>
+          <t>Rồi tao nghe nói về cuộc thi đấu võ đài ở Septimont. Một sân khấu nơi vô số câu chuyện sẽ được khai sinh! Sao tao có thể bỏ lỡ chứ?</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Nếu cậu đánh bại được ta, cậu đã trên đường trở thành huyền thoại tiếp theo rồi đấy.</t>
+          <t>Nếu cậu đánh bại được tao, cậu đã trên đường trở thành huyền thoại tiếp theo rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Haha, không đâu. Con đường đó không dành cho ta. Ta là một nghệ sĩ lang thang mà, nhớ không?</t>
+          <t>Haha, không đâu. Con đường đó không dành cho tao. Tao là một nghệ sĩ lang thang mà, nhớ không?</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Haha, đã chờ cậu lâu rồi đấy, đồng đội!</t>
+          <t>Haha, đã chờ mày lâu rồi đấy, đồng đội!</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đúng vậy! Ta muốn nghiên cứu chiêu thức của cậu... để tìm cách đánh bại cậu. Nhưng giờ thì... có vẻ không cần nữa rồi.</t>
+          <t>Đúng vậy! Tao muốn nghiên cứu chiêu thức của cậu... để tìm cách đánh bại cậu. Nhưng giờ thì... có vẻ không cần nữa rồi.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta sẽ dốc hết sức mình.</t>
+          <t>Tao sẽ dốc hết sức mình.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Ha! Ta cũng thế! Dù chỉ là trò chơi, ta cũng sẽ không nhượng bộ đâu!</t>
+          <t>Ha! Tao cũng thế! Dù chỉ là trò chơi, tao cũng sẽ không nhượng bộ đâu!</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Furius bảo anh ấy là người quen cũ của ta.</t>
+          <t>Furius bảo anh ấy là người quen cũ của tao.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Người bí ẩn à? Ta đâu có giấu giếm hắn đâu. Có lẽ hắn chỉ thích thêm chút kịch tính thôi.</t>
+          <t>Người bí ẩn à? Tao đâu có giấu giếm hắn đâu. Có lẽ hắn chỉ thích thêm chút kịch tính thôi.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Đúng ý ta luôn.</t>
+          <t>Đúng ý tao luôn.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Xin chào, {PlayerName}.</t>
+          <t>Chào {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Nhưng đã cả tháng trời rồi, cậu chẳng làm gì ngoài chơi Peaks of Prestige!</t>
+          <t>Nhưng đã cả tháng trời rồi, mày chẳng làm gì ngoài chơi Peaks of Prestige!</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Nhưng nếu ta thắng... ta sẽ chơi cả ngày luôn. Không phàn nàn, không học hành gì hết. Thỏa thuận thế nào?</t>
+          <t>Nhưng nếu tao thắng... tao sẽ chơi cả ngày luôn. Không phàn nàn, không học hành gì hết. Thỏa thuận thế nào?</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Tôi nghe tin rồi! {Male=Anh;Female=Chị} vừa đánh bại Lãnh Chúa Uy Danh thứ năm! Xin chúc mừng, {Male=anh;Female=chị} {PlayerName}!</t>
+          <t>Tôi nghe tin rồi! bạn vừa đánh bại Lãnh Chúa Uy Danh thứ năm! Xin chúc mừng, {Male=Mr.;Female=Ms.} {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Chúc mừng đã đánh bại Ngũ Đại Lãnh Chúa Uy Tín, {Male=Ngài;Female=Nữ sĩ} {PlayerName}!</t>
+          <t>Chúc mừng đã đánh bại Ngũ Đại Lãnh Chúa Uy Tín, {Male=Mr.;Female=Ms.} {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Chúc mừng đã đánh bại Ngũ Đại Lãnh Chúa Uy Tín, {Male=Ngài;Female=Nữ sĩ} {PlayerName}!</t>
+          <t>Chúc mừng đã đánh bại Ngũ Đại Lãnh Chúa Uy Tín, {Male=Mr.;Female=Ms.} {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Thật lòng, không phải vì ta muốn khoe khoang gì đâu...</t>
+          <t>Thật lòng, không phải vì tao muốn khoe khoang gì đâu...</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Thật lòng, dĩ nhiên ta muốn nó lan truyền và làm ta giàu sụ. Đó là lý do ta thuê Colosseum Olymdos và tổ chức một đêm chung kết hoành tráng.</t>
+          <t>Thật lòng, dĩ nhiên tao muốn nó lan truyền và làm tao giàu sụ. Đó là lý do tao thuê Colosseum Olymdos và tổ chức một đêm chung kết hoành tráng.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Lại đây, {Male=anh;Female=chị} {PlayerName}. Cho ta xem ngươi có gì nào.</t>
+          <t>Lại đây, {Male=Mr.;Female=Ms.} {PlayerName}. Cho ta xem ngươi có gì nào.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Một trận đấu tuyệt vời, {Male=ông;Female=bà} {PlayerName}.</t>
+          <t>Một trận đấu tuyệt vời, {Male=Mr.;Female=Ms.} {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -17929,7 +17929,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>{Male=Anh;Female=Chị} {PlayerName}, {Male=anh;Female=chị} có nghe thấy không?!</t>
+          <t>{Male=Mr.;Female=Ms.} {PlayerName}, bạn có nghe thấy không?!</t>
         </is>
       </c>
     </row>
@@ -18319,7 +18319,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Thật lòng, kết quả này vượt xa mọi mong đợi của ta.</t>
+          <t>Thật lòng, kết quả này vượt xa mọi mong đợi của tao.</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Cảm ơn cậu. Thật lòng đấy. Cảm ơn rất nhiều, {Male=anh;Female=chị} {PlayerName}.</t>
+          <t>Cảm ơn cậu. Thật lòng đấy. Cảm ơn rất nhiều, {Male=Mr.;Female=Ms.} {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Xin chào, {Male=anh;Female=chị} {PlayerName}! Đến để hỏi về Đỉnh Vinh Quang à?</t>
+          <t>Xin chào, {Male=Mr.;Female=Ms.} {PlayerName}! Đến để hỏi về Đỉnh Vinh Quang à?</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Hãy tham gia Đỉnh Cao Danh Vọng! Vô số tiếng vọng. Chiến thuật vô biên. Người tiếp theo có thể là Bậc Thầy Đấu Đỉnh!&lt;/b&gt;</t>
+          <t>&lt;b&gt;Hãy tham gia Đỉnh Cao Danh Vọng! Vô số Echo. Chiến thuật vô biên. Người tiếp theo có thể là Bậc Thầy Đấu Đỉnh!&lt;/b&gt;</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Ta nghe nói cậu đã trở thành ngôi sao lớn rồi nhỉ? Đến cả dân Solis cũng không ngớt lời khen đấy!</t>
+          <t>Tao nghe nói cậu đã trở thành ngôi sao lớn rồi nhỉ? Đến cả dân Solis cũng không ngớt lời khen đấy!</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Hahaha, ta thích cái sự tự tin này của ngươi. Chính cái đó làm chúng ta thành một đội!</t>
+          <t>Hahaha, tao thích cái sự tự tin này của mày. Chính cái đó làm chúng ta thành một đội!</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Haha! Ta đã biết ngươi có tiềm năng khủng khiếp ngay từ lần đầu giao đấu. Quả nhiên mắt ta tinh tường thật!</t>
+          <t>Haha! Tao đã biết mày có tiềm năng khủng khiếp ngay từ lần đầu giao đấu. Quả nhiên mắt tao tinh tường thật!</t>
         </is>
       </c>
     </row>
@@ -23519,7 +23519,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Thật lòng, ta không ngờ ngươi lại thực sự giành được quyền thách đấu với Kẻ Chinh Phục Danh Vọng đấy. Ta mừng cho ngươi lắm!</t>
+          <t>Thật lòng, tao không ngờ mày lại thực sự giành được quyền thách đấu với Kẻ Chinh Phục Danh Vọng đấy. Tao mừng cho mày lắm!</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Ta nghe nói cậu sắp có trận đấu lớn đấy. Thật tuyệt vời!</t>
+          <t>Tao nghe nói cậu sắp có trận đấu lớn đấy. Thật tuyệt vời!</t>
         </is>
       </c>
     </row>
@@ -27029,7 +27029,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>(Ôi không, ôi không... Nhìn {Male=anh ấy;Female=cô ấy} chiến đấu kìa... {Male=Anh ấy;Female=Cô ấy} đúng là một cỗ máy sức mạnh! T-Tôi không biết mình có thắng nổi không...)</t>
+          <t>(Ôi không, ôi không... Nhìn {Male=he;Female=she} chiến đấu kìa... {Male=he;Female=she} đúng là một cỗ máy sức mạnh! T-Tôi không biết mình có thắng nổi không...)</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Không cãi được... Rốt cuộc thì ta thua mà...</t>
+          <t>Không cãi được... Rốt cuộc thì tao thua mà...</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Nếu ta giúp cậu đánh bại chúng...</t>
+          <t>Nếu tao giúp cậu đánh bại chúng...</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Ui... chân ta... đời ta coi như xong rồi...</t>
+          <t>Ui... chân tao... đời tao coi như xong rồi...</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Thật lòng... Ta chưa bao giờ thấy Đỉnh Vinh Quang có gì thú vị cả.</t>
+          <t>Thật lòng... Tao chưa bao giờ thấy Đỉnh Vinh Quang có gì thú vị cả.</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Dù cậu đã giúp ta một việc, nhưng đừng mong ta sẽ nương tay với cậu đâu. Danh tiếng của ta đang bị đe dọa đó.</t>
+          <t>Dù cậu đã giúp tao một việc, nhưng đừng mong tao sẽ nương tay với cậu đâu. Danh tiếng của tao đang bị đe dọa đó.</t>
         </is>
       </c>
     </row>
@@ -30084,7 +30084,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Ta muốn thách đấu ngươi.</t>
+          <t>Tao muốn thách đấu mày.</t>
         </is>
       </c>
     </row>
@@ -30149,7 +30149,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Chưa được. Ta còn đang làm nhiệm vụ.</t>
+          <t>Chưa được. Tao còn đang làm nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Nếu không, ông chủ nhà sẽ vui vẻ trừ lương ta cả năm trời.</t>
+          <t>Nếu không, ông chủ nhà sẽ vui vẻ trừ lương tao cả năm trời.</t>
         </is>
       </c>
     </row>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Theo cái này... ta được nghỉ việc sau khoảng bốn năm nữa.</t>
+          <t>Theo cái này... tao được nghỉ việc sau khoảng bốn năm nữa.</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nhưng nếu cậu hứa không mách ta... thì mình có thể đấu một trận.</t>
+          <t>Nhưng nếu cậu hứa không mách tao... thì mình có thể đấu một trận.</t>
         </is>
       </c>
     </row>
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Nếu ta báo cáo được vài đứa, có khi còn lĩnh thêm tiền thưởng cả tháng.</t>
+          <t>Nếu tao báo cáo được vài đứa, có khi còn lĩnh thêm tiền thưởng cả tháng.</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Tin tốt là, thắng hay thua thì ta vẫn được trả công như nhau.</t>
+          <t>Tin tốt là, thắng hay thua thì tao vẫn được trả công như nhau.</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Tin xấu là... ta vẫn còn thiếu tám trăm bảy mươi nghìn.</t>
+          <t>Tin xấu là... tao vẫn còn thiếu tám trăm bảy mươi nghìn.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đó là số tiền ta cần để nghỉ việc này mãi mãi.</t>
+          <t>Đó là số tiền tao cần để nghỉ việc này mãi mãi.</t>
         </is>
       </c>
     </row>
@@ -32749,7 +32749,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Lãnh Chúa Danh Vọng tiếp theo đang ở gần &lt;te href=850172&gt;Cliffside Harbor&lt;/te&gt;. Hãy đến đó.</t>
+          <t>Lãnh Chúa Danh Vọng tiếp theo đang ở gần &lt;te href=850172&gt;Cảng Vách Đá&lt;/te&gt;. Hãy đến đó.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Thỉnh thoảng ta cũng cảm nhận được luồng mệt mỏi y chang Zani...</t>
+          <t>Thỉnh thoảng tao cũng cảm nhận được luồng mệt mỏi y chang Zani...</t>
         </is>
       </c>
     </row>
